--- a/examples/本地验收报告/网络部督办报告.xlsx
+++ b/examples/本地验收报告/网络部督办报告.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:09+08:00</t>
+          <t>2026-10-17T15:27:04+08:00</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1515,7 +1515,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>尚未研判</t>
+          <t>信息不足</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1777,12 +1777,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>a42ef86345fc4f7eae3675df1a4557c8</t>
+          <t>7799a40856de4b5693bd5315fe523083</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试园区扩容</t>
+          <t>测试原生网络部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1804,34 +1804,54 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>办理中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:55+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
@@ -1842,17 +1862,17 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
